--- a/artfynd/A 1762-2026 artfynd.xlsx
+++ b/artfynd/A 1762-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65481840</v>
+        <v>69018074</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jörn, Vb</t>
+          <t>Storträsk, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733203.1011089198</v>
+        <v>733201</v>
       </c>
       <c r="R2" t="n">
-        <v>7237213.016263354</v>
+        <v>7237221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -741,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65481838</v>
+        <v>65481834</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733240.8272221353</v>
+        <v>733399</v>
       </c>
       <c r="R3" t="n">
-        <v>7237227.393428374</v>
+        <v>7237018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,19 +844,9 @@
           <t>2016-07-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65481836</v>
+        <v>65481838</v>
       </c>
       <c r="B4" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,19 +884,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733312.7505054208</v>
+        <v>733241</v>
       </c>
       <c r="R4" t="n">
-        <v>7237092.5794521</v>
+        <v>7237227</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,19 +941,9 @@
           <t>2016-07-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-07-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>65481834</v>
+        <v>65481835</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,23 +981,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733398.5378110578</v>
+        <v>733349</v>
       </c>
       <c r="R5" t="n">
-        <v>7237017.511110448</v>
+        <v>7237102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,19 +1034,9 @@
           <t>2016-07-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-07-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69017658</v>
+        <v>65481836</v>
       </c>
       <c r="B6" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,14 +1090,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storträsk, Vb</t>
+          <t>Jörn, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733192.0535065482</v>
+        <v>733313</v>
       </c>
       <c r="R6" t="n">
-        <v>7237213.829946714</v>
+        <v>7237093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,22 +1124,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,31 +1144,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69017666</v>
+        <v>65481840</v>
       </c>
       <c r="B7" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,14 +1183,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storträsk, Vb</t>
+          <t>Jörn, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733309.1480985363</v>
+        <v>733203</v>
       </c>
       <c r="R7" t="n">
-        <v>7237298.199048083</v>
+        <v>7237213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,22 +1217,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,55 +1237,42 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69018074</v>
+        <v>69017658</v>
       </c>
       <c r="B8" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1280,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733201.211385207</v>
+        <v>733192</v>
       </c>
       <c r="R8" t="n">
-        <v>7237220.883427178</v>
+        <v>7237214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,19 +1313,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-07-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,6 +1339,103 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>69017666</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>733309</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7237298</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-07-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-07-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 1762-2026 artfynd.xlsx
+++ b/artfynd/A 1762-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018074</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65481834</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65481838</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65481835</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1153,6 +1178,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65481836</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1246,6 +1276,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65481840</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1343,6 +1378,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69017658</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1440,8 +1480,23 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69017666</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>